--- a/词语表模板.xlsx
+++ b/词语表模板.xlsx
@@ -1,50 +1,118 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s8930779a\Downloads\20261028trial-main\20261028trial-main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DC812E-CA9F-4420-9C11-D4F5B6C2F6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="词语表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="怎么用" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="词语表" sheetId="1" r:id="rId1"/>
+    <sheet name="怎么用" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>词语</t>
+  </si>
+  <si>
+    <t>把「词语表」那一页的内容换成你自己单元的词语就好。</t>
+  </si>
+  <si>
+    <t>1. 第一行（词语 / 释义）请不要动。</t>
+  </si>
+  <si>
+    <t>2. 一行一个词语。至少 8 个，越多越好（最少 4 个）。</t>
+  </si>
+  <si>
+    <t>3. 错误选项不用你写，程序会自动从其他词语的释义里抓。</t>
+  </si>
+  <si>
+    <t>4. 存档之后，把这个档案连同游戏资料夹一起上传到 Claude，</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   再把资源页上的提示词贴进去，就会帮你改好。</t>
+  </si>
+  <si>
+    <t>资源页：https://kaixinbuilds.github.io/2026AIinSecCLNLC.html</t>
+  </si>
+  <si>
+    <t>纷纷扰扰</t>
+  </si>
+  <si>
+    <t>干干净净</t>
+  </si>
+  <si>
+    <t>平平安安</t>
+  </si>
+  <si>
+    <t>拖拖拉拉</t>
+  </si>
+  <si>
+    <t>吞吞吐吐</t>
+  </si>
+  <si>
+    <t>意思</t>
+  </si>
+  <si>
+    <t>事情繁多而杂乱，让人不得安宁。</t>
+  </si>
+  <si>
+    <t>没有灰尘、污垢，非常清洁。</t>
+  </si>
+  <si>
+    <t>平安无事，没有遇到危险或意外。</t>
+  </si>
+  <si>
+    <t>做事慢吞吞，不抓紧时间。</t>
+  </si>
+  <si>
+    <t>说话不干脆，想说又不敢说的样子。</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0096521F"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -60,87 +128,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -428,125 +437,70 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>词语</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>释义</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>维护</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>保持、保障，使不受破坏</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>策略</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>为了达到某个目标而定下的计划或方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>催促</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>叫人赶快行动，不要拖延</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>沉浸</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>完全进入某种境界或思想活动中</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>渲染</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>夸大地形容，使气氛更浓</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>斟酌</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>反复考虑，仔细掂量是否合适</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>潜移默化</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>在不知不觉中受到影响而发生变化</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>锲而不舍</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>一直刻下去不放手，比喻有恒心、不放弃</t>
-        </is>
-      </c>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -554,70 +508,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>把「词语表」那一页的内容换成你自己单元的词语就好。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1. 第一行（词语 / 释义）请不要动。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2. 一行一个词语。至少 8 个，越多越好（最少 4 个）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3. 错误选项不用你写，程序会自动从其他词语的释义里抓。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4. 存档之后，把这个档案连同游戏资料夹一起上传到 Claude，</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   再把资源页上的提示词贴进去，就会帮你改好。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>资源页：https://kaixinbuilds.github.io/2026AIinSecCLNLC.html</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
